--- a/wombat_Y2SiO5_example/Y2SiO5_reflections_angles.xlsx
+++ b/wombat_Y2SiO5_example/Y2SiO5_reflections_angles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>two theta (deg)</t>
+          <t>A4 (deg)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -459,6 +459,11 @@
           <t>z (m)</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>two theta (deg)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -481,6 +486,9 @@
       </c>
       <c r="G2" t="n">
         <v>-0.79931</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10.69134</v>
       </c>
     </row>
     <row r="3">
@@ -505,36 +513,42 @@
       <c r="G3" t="n">
         <v>-0</v>
       </c>
+      <c r="H3" t="n">
+        <v>48.90247</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="E4" t="n">
-        <v>-116.87136</v>
+        <v>15.68452</v>
       </c>
       <c r="F4" t="n">
-        <v>-72.072</v>
+        <v>-56.25807</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.00829</v>
+        <v>-0.031</v>
+      </c>
+      <c r="H4" t="n">
+        <v>56.25807</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -543,13 +557,16 @@
         <v>-4</v>
       </c>
       <c r="E5" t="n">
-        <v>15.68452</v>
+        <v>31.44333</v>
       </c>
       <c r="F5" t="n">
-        <v>-56.25807</v>
+        <v>-66.2405</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.031</v>
+        <v>-0.01784</v>
+      </c>
+      <c r="H5" t="n">
+        <v>66.2405</v>
       </c>
     </row>
     <row r="6">
@@ -557,19 +574,176 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-34.25322</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-66.91202</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.04416</v>
+      </c>
+      <c r="H6" t="n">
+        <v>66.91202</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="n">
         <v>4</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-116.87136</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-72.072</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.00829</v>
+      </c>
+      <c r="H7" t="n">
+        <v>72.072</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.22973</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-94.33637</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.02658</v>
+      </c>
+      <c r="H8" t="n">
+        <v>94.33637</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-170.48089</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-110.08894</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="H9" t="n">
+        <v>110.08894</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-147.51378</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-111.75441</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>111.75441</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-80.80262999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-113.31102</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="H11" t="n">
+        <v>113.31102</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
         <v>0.0045</v>
       </c>
+      <c r="H12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/wombat_Y2SiO5_example/Y2SiO5_reflections_angles.xlsx
+++ b/wombat_Y2SiO5_example/Y2SiO5_reflections_angles.xlsx
@@ -1,37 +1,69 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\wombat_instrument_work\eulerian_cradle\Wombat_DMCpy\wombat_Y2SiO5_example\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18546974-2A28-408D-A5BD-282B4D5AF71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="6435" yWindow="1440" windowWidth="21600" windowHeight="12510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>A3 (deg)</t>
+  </si>
+  <si>
+    <t>A4 (deg)</t>
+  </si>
+  <si>
+    <t>z (m)</t>
+  </si>
+  <si>
+    <t>two theta (deg)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +78,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,330 +402,317 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>A3 (deg)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>A4 (deg)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>z (m)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>two theta (deg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-68.61376</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-68.613759999999999</v>
+      </c>
+      <c r="F2">
         <v>-10.69134</v>
       </c>
-      <c r="G2" t="n">
-        <v>-0.79931</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="G2">
+        <v>-0.79930999999999996</v>
+      </c>
+      <c r="H2">
         <v>10.69134</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>-116.08781</v>
       </c>
-      <c r="F3" t="n">
-        <v>-48.90247</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>48.90247</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="F3">
+        <v>-48.902470000000001</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>48.902470000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>-4</v>
       </c>
-      <c r="E4" t="n">
-        <v>15.68452</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-56.25807</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.031</v>
-      </c>
-      <c r="H4" t="n">
-        <v>56.25807</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="E4">
+        <v>15.684519999999999</v>
+      </c>
+      <c r="F4">
+        <v>-56.258069999999996</v>
+      </c>
+      <c r="G4">
+        <v>-3.1E-2</v>
+      </c>
+      <c r="H4">
+        <v>56.258069999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>-4</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>31.44333</v>
       </c>
-      <c r="F5" t="n">
-        <v>-66.2405</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.01784</v>
-      </c>
-      <c r="H5" t="n">
-        <v>66.2405</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="F5">
+        <v>-66.240499999999997</v>
+      </c>
+      <c r="G5">
+        <v>-1.7840000000000002E-2</v>
+      </c>
+      <c r="H5">
+        <v>66.240499999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>6</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>-4</v>
       </c>
-      <c r="E6" t="n">
-        <v>-34.25322</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-66.91202</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.04416</v>
-      </c>
-      <c r="H6" t="n">
-        <v>66.91202</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="E6">
+        <v>-34.253219999999999</v>
+      </c>
+      <c r="F6">
+        <v>-66.912019999999998</v>
+      </c>
+      <c r="G6">
+        <v>-4.4159999999999998E-2</v>
+      </c>
+      <c r="H6">
+        <v>66.912019999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>2</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>-116.87136</v>
       </c>
-      <c r="F7" t="n">
-        <v>-72.072</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.00829</v>
-      </c>
-      <c r="H7" t="n">
-        <v>72.072</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="F7">
+        <v>-72.072000000000003</v>
+      </c>
+      <c r="G7">
+        <v>-8.2900000000000005E-3</v>
+      </c>
+      <c r="H7">
+        <v>72.072000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>-6</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>4.22973</v>
       </c>
-      <c r="F8" t="n">
-        <v>-94.33637</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.02658</v>
-      </c>
-      <c r="H8" t="n">
-        <v>94.33637</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="F8">
+        <v>-94.336370000000002</v>
+      </c>
+      <c r="G8">
+        <v>-2.6579999999999999E-2</v>
+      </c>
+      <c r="H8">
+        <v>94.336370000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>6</v>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>-170.48089</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-110.08894</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01784</v>
-      </c>
-      <c r="H9" t="n">
-        <v>110.08894</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="E9">
+        <v>-170.48088999999999</v>
+      </c>
+      <c r="F9">
+        <v>-110.08893999999999</v>
+      </c>
+      <c r="G9">
+        <v>1.7840000000000002E-2</v>
+      </c>
+      <c r="H9">
+        <v>110.08893999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>4</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>-147.51378</v>
       </c>
-      <c r="F10" t="n">
-        <v>-111.75441</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>111.75441</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="F10">
+        <v>-111.75440999999999</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>111.75440999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <v>-4</v>
       </c>
-      <c r="E11" t="n">
-        <v>-80.80262999999999</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="E11">
+        <v>-80.802629999999994</v>
+      </c>
+      <c r="F11">
         <v>-113.31102</v>
       </c>
-      <c r="G11" t="n">
-        <v>-0.0408</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="G11">
+        <v>-4.0800000000000003E-2</v>
+      </c>
+      <c r="H11">
         <v>113.31102</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
         <v>6</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12">
+        <v>4.4999999999999997E-3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/wombat_Y2SiO5_example/Y2SiO5_reflections_angles.xlsx
+++ b/wombat_Y2SiO5_example/Y2SiO5_reflections_angles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\wombat_instrument_work\eulerian_cradle\Wombat_DMCpy\wombat_Y2SiO5_example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18546974-2A28-408D-A5BD-282B4D5AF71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A8FA2B-2345-4A05-BE93-D476D2AA9330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6435" yWindow="1440" windowWidth="21600" windowHeight="12510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2415" yWindow="2160" windowWidth="21600" windowHeight="12510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -406,12 +406,8 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -451,16 +447,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>-68.613759999999999</v>
+        <v>111.13418</v>
       </c>
       <c r="F2">
-        <v>-10.69134</v>
+        <v>-11.28567</v>
       </c>
       <c r="G2">
-        <v>-0.79930999999999996</v>
+        <v>-0.77851999999999999</v>
       </c>
       <c r="H2">
-        <v>10.69134</v>
+        <v>11.28567</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -477,16 +473,16 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>-116.08781</v>
+        <v>63.783470000000001</v>
       </c>
       <c r="F3">
-        <v>-48.902470000000001</v>
+        <v>-48.88702</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1.7729999999999999E-2</v>
       </c>
       <c r="H3">
-        <v>48.902470000000001</v>
+        <v>48.88702</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -503,16 +499,16 @@
         <v>-4</v>
       </c>
       <c r="E4">
-        <v>15.684519999999999</v>
+        <v>-164.50511</v>
       </c>
       <c r="F4">
-        <v>-56.258069999999996</v>
+        <v>-56.238849999999999</v>
       </c>
       <c r="G4">
-        <v>-3.1E-2</v>
+        <v>-3.5959999999999999E-2</v>
       </c>
       <c r="H4">
-        <v>56.258069999999996</v>
+        <v>56.238849999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -529,16 +525,16 @@
         <v>-4</v>
       </c>
       <c r="E5">
-        <v>31.44333</v>
+        <v>-148.70690999999999</v>
       </c>
       <c r="F5">
-        <v>-66.240499999999997</v>
+        <v>-66.200940000000003</v>
       </c>
       <c r="G5">
-        <v>-1.7840000000000002E-2</v>
+        <v>-2.9649999999999999E-2</v>
       </c>
       <c r="H5">
-        <v>66.240499999999997</v>
+        <v>66.200940000000003</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -555,16 +551,16 @@
         <v>-4</v>
       </c>
       <c r="E6">
-        <v>-34.253219999999999</v>
+        <v>145.51604</v>
       </c>
       <c r="F6">
-        <v>-66.912019999999998</v>
+        <v>-66.971289999999996</v>
       </c>
       <c r="G6">
-        <v>-4.4159999999999998E-2</v>
+        <v>-3.3489999999999999E-2</v>
       </c>
       <c r="H6">
-        <v>66.912019999999998</v>
+        <v>66.971289999999996</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -581,16 +577,16 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>-116.87136</v>
+        <v>63.003720000000001</v>
       </c>
       <c r="F7">
-        <v>-72.072000000000003</v>
+        <v>-72.067570000000003</v>
       </c>
       <c r="G7">
-        <v>-8.2900000000000005E-3</v>
+        <v>1.1180000000000001E-2</v>
       </c>
       <c r="H7">
-        <v>72.072000000000003</v>
+        <v>72.067570000000003</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -607,16 +603,16 @@
         <v>-6</v>
       </c>
       <c r="E8">
-        <v>4.22973</v>
+        <v>-175.93306999999999</v>
       </c>
       <c r="F8">
-        <v>-94.336370000000002</v>
+        <v>-94.282589999999999</v>
       </c>
       <c r="G8">
-        <v>-2.6579999999999999E-2</v>
+        <v>-3.4169999999999999E-2</v>
       </c>
       <c r="H8">
-        <v>94.336370000000002</v>
+        <v>94.282589999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -633,16 +629,16 @@
         <v>6</v>
       </c>
       <c r="E9">
-        <v>-170.48088999999999</v>
+        <v>9.3924400000000006</v>
       </c>
       <c r="F9">
-        <v>-110.08893999999999</v>
+        <v>-110.00223</v>
       </c>
       <c r="G9">
-        <v>1.7840000000000002E-2</v>
+        <v>2.9649999999999999E-2</v>
       </c>
       <c r="H9">
-        <v>110.08893999999999</v>
+        <v>110.00223</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -659,16 +655,16 @@
         <v>4</v>
       </c>
       <c r="E10">
-        <v>-147.51378</v>
+        <v>32.374839999999999</v>
       </c>
       <c r="F10">
-        <v>-111.75440999999999</v>
+        <v>-111.70426999999999</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1.7729999999999999E-2</v>
       </c>
       <c r="H10">
-        <v>111.75440999999999</v>
+        <v>111.70426999999999</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -685,16 +681,16 @@
         <v>-4</v>
       </c>
       <c r="E11">
-        <v>-80.802629999999994</v>
+        <v>98.938720000000004</v>
       </c>
       <c r="F11">
-        <v>-113.31102</v>
+        <v>-113.49097</v>
       </c>
       <c r="G11">
-        <v>-4.0800000000000003E-2</v>
+        <v>-2.392E-2</v>
       </c>
       <c r="H11">
-        <v>113.31102</v>
+        <v>113.49097</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -711,7 +707,7 @@
         <v>6</v>
       </c>
       <c r="G12">
-        <v>4.4999999999999997E-3</v>
+        <v>2.103E-2</v>
       </c>
     </row>
   </sheetData>

--- a/wombat_Y2SiO5_example/Y2SiO5_reflections_angles.xlsx
+++ b/wombat_Y2SiO5_example/Y2SiO5_reflections_angles.xlsx
@@ -1,37 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\wombat_instrument_work\DMCpy_for_wombat\Wombat_DMCpy\wombat_Y2SiO5_example\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821F75C6-CE7A-45BF-A838-1CD18583ECE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-23070" yWindow="3450" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>A3 (deg)</t>
+  </si>
+  <si>
+    <t>A4 (deg)</t>
+  </si>
+  <si>
+    <t>z (m)</t>
+  </si>
+  <si>
+    <t>two theta (deg)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +91,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,330 +415,312 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>A3 (deg)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>A4 (deg)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>z (m)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>two theta (deg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>111.13418</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>-11.28567</v>
       </c>
-      <c r="G2" t="n">
-        <v>-0.77852</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="G2">
+        <v>-0.77851999999999999</v>
+      </c>
+      <c r="H2">
         <v>11.28567</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
-        <v>63.78347</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3">
+        <v>63.783470000000001</v>
+      </c>
+      <c r="F3">
         <v>-48.88702</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.01773</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="G3">
+        <v>1.7729999999999999E-2</v>
+      </c>
+      <c r="H3">
         <v>48.88702</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>-4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>-164.50511</v>
       </c>
-      <c r="F4" t="n">
-        <v>-56.23885</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.03596</v>
-      </c>
-      <c r="H4" t="n">
-        <v>56.23885</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="F4">
+        <v>-56.238849999999999</v>
+      </c>
+      <c r="G4">
+        <v>-3.5959999999999999E-2</v>
+      </c>
+      <c r="H4">
+        <v>56.238849999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>-4</v>
       </c>
-      <c r="E5" t="n">
-        <v>-148.70691</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-66.20094</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.02965</v>
-      </c>
-      <c r="H5" t="n">
-        <v>66.20094</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="E5">
+        <v>-148.70690999999999</v>
+      </c>
+      <c r="F5">
+        <v>-66.200940000000003</v>
+      </c>
+      <c r="G5">
+        <v>-2.9649999999999999E-2</v>
+      </c>
+      <c r="H5">
+        <v>66.200940000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>6</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>-4</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>145.51604</v>
       </c>
-      <c r="F6" t="n">
-        <v>-66.97129</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.03349</v>
-      </c>
-      <c r="H6" t="n">
-        <v>66.97129</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="F6">
+        <v>-66.971289999999996</v>
+      </c>
+      <c r="G6">
+        <v>-3.3489999999999999E-2</v>
+      </c>
+      <c r="H6">
+        <v>66.971289999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>2</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
-        <v>63.00372</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-72.06757</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.01118</v>
-      </c>
-      <c r="H7" t="n">
-        <v>72.06757</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="E7">
+        <v>63.003720000000001</v>
+      </c>
+      <c r="F7">
+        <v>-72.067570000000003</v>
+      </c>
+      <c r="G7">
+        <v>1.1180000000000001E-2</v>
+      </c>
+      <c r="H7">
+        <v>72.067570000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>-6</v>
       </c>
-      <c r="E8" t="n">
-        <v>-175.93307</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-94.28259</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.03417</v>
-      </c>
-      <c r="H8" t="n">
-        <v>94.28259</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="E8">
+        <v>-175.93306999999999</v>
+      </c>
+      <c r="F8">
+        <v>-94.282589999999999</v>
+      </c>
+      <c r="G8">
+        <v>-3.4169999999999999E-2</v>
+      </c>
+      <c r="H8">
+        <v>94.282589999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>6</v>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>9.392440000000001</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9">
+        <v>9.3924400000000006</v>
+      </c>
+      <c r="F9">
         <v>-110.00223</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.02965</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G9">
+        <v>2.9649999999999999E-2</v>
+      </c>
+      <c r="H9">
         <v>110.00223</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>4</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" t="n">
-        <v>32.37484</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-111.70427</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.01773</v>
-      </c>
-      <c r="H10" t="n">
-        <v>111.70427</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="E10">
+        <v>32.374839999999999</v>
+      </c>
+      <c r="F10">
+        <v>-111.70426999999999</v>
+      </c>
+      <c r="G10">
+        <v>1.7729999999999999E-2</v>
+      </c>
+      <c r="H10">
+        <v>111.70426999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <v>-4</v>
       </c>
-      <c r="E11" t="n">
-        <v>98.93872</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="E11">
+        <v>98.938720000000004</v>
+      </c>
+      <c r="F11">
         <v>-113.49097</v>
       </c>
-      <c r="G11" t="n">
-        <v>-0.02392</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="G11">
+        <v>-2.392E-2</v>
+      </c>
+      <c r="H11">
         <v>113.49097</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
         <v>6</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
-        <v>0.02103</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12">
+        <v>2.103E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
